--- a/Configs/GameConfig/Datas/deck.xlsx
+++ b/Configs/GameConfig/Datas/deck.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95b1e0d95a3746f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a97cab531a94107"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -358,24 +358,12 @@
       <x:c r="B1" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" t="str">
-        <x:v>mode</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>minimalMode</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>baseSoldierTexts</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>handSize</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>defaultLevel</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>baseUnitCost</x:v>
-      </x:c>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -384,48 +372,26 @@
       <x:c r="B2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>(list#sep=,),string</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3" t="str">
-        <x:v>牌组模式(minimal/standard)</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>是否最简模式</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>基础兵字表(最简四兵)</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>手牌大小</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>默认等级</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>基础单位消耗</x:v>
-      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>占位</x:v>
+      </x:c>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -434,9 +400,7 @@
       <x:c r="B4"/>
       <x:c r="C4"/>
       <x:c r="D4"/>
-      <x:c r="E4" t="str">
-        <x:v>c</x:v>
-      </x:c>
+      <x:c r="E4"/>
       <x:c r="F4"/>
       <x:c r="G4"/>
       <x:c r="H4"/>
@@ -446,24 +410,12 @@
       <x:c r="B5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>minimal</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>刀,弓,枪,骑</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
